--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -15267,7 +15267,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de matrícula población de 0 a 24 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -2092,7 +2092,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:35</t>
+    <t xml:space="preserve">2026-09-07 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2021.xlsx
@@ -2092,7 +2092,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:48</t>
+    <t xml:space="preserve">2026-09-08 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
